--- a/data/trans_dic/P56$privada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,58</t>
+          <t>0,0; 42,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,23</t>
+          <t>0,0; 26,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 36,54</t>
+          <t>12,49; 38,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 45,64</t>
+          <t>5,85; 45,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 21,43</t>
+          <t>2,42; 21,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 32,93</t>
+          <t>5,88; 34,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,64; 25,33</t>
+          <t>12,23; 25,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 34,25</t>
+          <t>6,11; 33,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 17,08</t>
+          <t>1,86; 16,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 27,77</t>
+          <t>6,16; 25,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,14; 25,91</t>
+          <t>14,13; 26,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 34,52</t>
+          <t>6,59; 34,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 41,23</t>
+          <t>8,21; 42,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 20,02</t>
+          <t>2,52; 20,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 24,39</t>
+          <t>6,36; 23,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,56</t>
+          <t>0,0; 19,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 24,41</t>
+          <t>11,5; 24,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 22,18</t>
+          <t>8,53; 23,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 21,56</t>
+          <t>4,26; 21,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,09; 20,22</t>
+          <t>10,24; 20,62</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,66</t>
+          <t>0,0; 31,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 27,72</t>
+          <t>2,9; 28,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,4</t>
+          <t>0,0; 34,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,68; 34,14</t>
+          <t>7,85; 35,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 37,02</t>
+          <t>7,24; 35,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,31; 31,09</t>
+          <t>11,97; 31,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,28</t>
+          <t>0,0; 23,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 26,26</t>
+          <t>4,29; 27,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 28,84</t>
+          <t>6,84; 29,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 24,75</t>
+          <t>10,64; 26,08</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,31</t>
+          <t>0,0; 37,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,79</t>
+          <t>0,0; 27,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 28,67</t>
+          <t>8,51; 28,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 35,58</t>
+          <t>6,9; 34,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 32,75</t>
+          <t>8,29; 32,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,79; 34,3</t>
+          <t>9,23; 34,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,42; 26,26</t>
+          <t>12,29; 25,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 30,39</t>
+          <t>7,36; 29,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 27,63</t>
+          <t>7,5; 25,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 29,83</t>
+          <t>8,78; 28,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,98; 23,68</t>
+          <t>13,19; 24,06</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 16,46</t>
+          <t>1,77; 16,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 17,28</t>
+          <t>3,93; 18,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 22,84</t>
+          <t>7,05; 22,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 21,04</t>
+          <t>10,34; 21,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 19,65</t>
+          <t>5,63; 19,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 20,84</t>
+          <t>9,85; 19,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 22,64</t>
+          <t>9,59; 22,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 21,71</t>
+          <t>15,01; 22,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,98</t>
+          <t>6,11; 16,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 18,01</t>
+          <t>9,01; 17,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 20,07</t>
+          <t>10,64; 20,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 20,3</t>
+          <t>14,44; 20,36</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5443</t>
+          <t>0; 5535</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1808</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5736</t>
+          <t>0; 5109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3002; 9169</t>
+          <t>3134; 9725</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>952; 7480</t>
+          <t>958; 7439</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1054; 9883</t>
+          <t>1114; 10063</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2380; 13111</t>
+          <t>2342; 13749</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7817; 15664</t>
+          <t>7564; 15491</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1824; 10097</t>
+          <t>1801; 9730</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1061; 9683</t>
+          <t>1054; 9579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4206; 16327</t>
+          <t>3619; 15245</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12290; 22529</t>
+          <t>12287; 22639</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2084; 11184</t>
+          <t>2135; 11312</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1607; 8039</t>
+          <t>1601; 8211</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>543; 4890</t>
+          <t>616; 4894</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2084</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4233; 16015</t>
+          <t>4174; 15293</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 8855</t>
+          <t>0; 7983</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7727; 16336</t>
+          <t>7697; 16518</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2022</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8253; 21747</t>
+          <t>8360; 22654</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2875; 13059</t>
+          <t>2579; 13025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9220; 18469</t>
+          <t>9355; 18833</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1443</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2192</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5742</t>
+          <t>0; 5610</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>563; 5626</t>
+          <t>588; 5815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5717</t>
+          <t>0; 6004</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3240; 14406</t>
+          <t>3311; 14864</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2516; 12974</t>
+          <t>2539; 12346</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5199; 13126</t>
+          <t>5055; 13095</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6219</t>
+          <t>0; 5776</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3202; 14750</t>
+          <t>2408; 15184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3492; 15180</t>
+          <t>3600; 15586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6423; 15475</t>
+          <t>6653; 16308</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4949</t>
+          <t>0; 4942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6419</t>
+          <t>0; 5898</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6189</t>
+          <t>0; 6191</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2751; 9243</t>
+          <t>2742; 9219</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2250; 11435</t>
+          <t>2219; 11246</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4359; 16792</t>
+          <t>4251; 16772</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5468; 19158</t>
+          <t>5153; 19340</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9943; 21020</t>
+          <t>9840; 20335</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3244; 13797</t>
+          <t>3343; 13421</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5789; 20120</t>
+          <t>5458; 18659</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6490; 21446</t>
+          <t>6310; 20749</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14575; 26595</t>
+          <t>14809; 27019</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>858; 7949</t>
+          <t>854; 7968</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3142; 13566</t>
+          <t>3089; 14249</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5299; 16468</t>
+          <t>5085; 16395</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10000; 21474</t>
+          <t>10552; 22156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5480; 18381</t>
+          <t>5267; 18327</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20026; 42779</t>
+          <t>20218; 40510</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16591; 38885</t>
+          <t>16480; 39014</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37439; 54507</t>
+          <t>37689; 56308</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8182; 22663</t>
+          <t>8667; 23499</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27548; 51117</t>
+          <t>25556; 49965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24973; 48944</t>
+          <t>25946; 51109</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50756; 71672</t>
+          <t>50999; 71897</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$privada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,28</t>
+          <t>0,0; 37,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,93</t>
+          <t>0,0; 27,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 38,75</t>
+          <t>12,75; 38,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 45,39</t>
+          <t>5,78; 45,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 21,82</t>
+          <t>2,51; 22,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 34,53</t>
+          <t>5,87; 33,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 25,05</t>
+          <t>12,6; 25,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 33,01</t>
+          <t>6,27; 33,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 16,89</t>
+          <t>1,89; 18,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 25,93</t>
+          <t>6,0; 26,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,13; 26,04</t>
+          <t>14,13; 26,92</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 34,92</t>
+          <t>5,66; 34,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,21; 42,11</t>
+          <t>8,43; 44,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 20,04</t>
+          <t>2,07; 19,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 23,29</t>
+          <t>6,38; 23,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,44</t>
+          <t>0,0; 20,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 24,69</t>
+          <t>11,06; 24,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 23,1</t>
+          <t>8,6; 23,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 21,51</t>
+          <t>4,72; 22,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 20,62</t>
+          <t>10,12; 20,04</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,91</t>
+          <t>0,0; 28,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 28,65</t>
+          <t>3,07; 28,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,02</t>
+          <t>0,0; 35,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 35,22</t>
+          <t>7,29; 33,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 35,22</t>
+          <t>7,06; 37,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,97; 31,01</t>
+          <t>11,45; 30,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,48</t>
+          <t>0,0; 25,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 27,03</t>
+          <t>5,53; 26,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 29,61</t>
+          <t>6,67; 28,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 26,08</t>
+          <t>10,41; 25,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,25</t>
+          <t>0,0; 37,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,38</t>
+          <t>0,0; 30,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,58</t>
+          <t>0,0; 37,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 28,59</t>
+          <t>8,6; 28,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 34,99</t>
+          <t>3,79; 35,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 32,71</t>
+          <t>8,59; 31,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 34,63</t>
+          <t>9,01; 34,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 25,4</t>
+          <t>12,55; 26,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 29,56</t>
+          <t>6,88; 30,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 25,62</t>
+          <t>8,82; 27,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,78; 28,86</t>
+          <t>8,75; 30,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,19; 24,06</t>
+          <t>12,85; 24,83</t>
         </is>
       </c>
     </row>
@@ -1224,47 +1224,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>14,89%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14,89%</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,5</t>
+          <t>1,84; 16,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 18,15</t>
+          <t>4,05; 18,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 22,74</t>
+          <t>7,12; 22,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,71</t>
+          <t>10,05; 21,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,63; 19,59</t>
+          <t>5,61; 20,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 19,74</t>
+          <t>9,59; 20,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 22,71</t>
+          <t>9,47; 23,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,01; 22,43</t>
+          <t>14,93; 21,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,57</t>
+          <t>5,55; 16,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 17,61</t>
+          <t>9,24; 17,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,64; 20,96</t>
+          <t>10,5; 20,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 20,36</t>
+          <t>14,4; 20,51</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>18202</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5535</t>
+          <t>0; 4885</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1655,52 +1655,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5109</t>
+          <t>0; 5219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3134; 9725</t>
+          <t>3327; 9989</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>958; 7439</t>
+          <t>948; 7481</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1114; 10063</t>
+          <t>1158; 10397</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2342; 13749</t>
+          <t>2338; 13416</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7564; 15491</t>
+          <t>8288; 16709</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1801; 9730</t>
+          <t>1848; 10000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1054; 9579</t>
+          <t>1070; 10565</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3619; 15245</t>
+          <t>3527; 15485</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12287; 22639</t>
+          <t>12986; 24736</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>14490</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2135; 11312</t>
+          <t>1832; 11128</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1601; 8211</t>
+          <t>1644; 8710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>616; 4894</t>
+          <t>543; 5046</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4174; 15293</t>
+          <t>4190; 15459</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7983</t>
+          <t>0; 8533</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7697; 16518</t>
+          <t>8188; 17881</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8360; 22654</t>
+          <t>8433; 22653</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2579; 13025</t>
+          <t>2861; 13724</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9355; 18833</t>
+          <t>10146; 20101</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>11815</t>
         </is>
       </c>
     </row>
@@ -2071,52 +2071,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5610</t>
+          <t>0; 5084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>588; 5815</t>
+          <t>710; 6570</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6004</t>
+          <t>0; 6178</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3311; 14864</t>
+          <t>3077; 14216</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2539; 12346</t>
+          <t>2475; 13013</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5055; 13095</t>
+          <t>5461; 14419</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5776</t>
+          <t>0; 6155</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2408; 15184</t>
+          <t>3106; 15072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3600; 15586</t>
+          <t>3509; 15019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6653; 16308</t>
+          <t>7370; 17795</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>21497</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4942</t>
+          <t>0; 4950</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5898</t>
+          <t>0; 6495</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6191</t>
+          <t>0; 6086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2742; 9219</t>
+          <t>2847; 9464</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2219; 11246</t>
+          <t>1219; 11255</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4251; 16772</t>
+          <t>4403; 16226</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5153; 19340</t>
+          <t>5034; 19456</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9840; 20335</t>
+          <t>11036; 23275</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3343; 13421</t>
+          <t>3124; 13732</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5458; 18659</t>
+          <t>6424; 19838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6310; 20749</t>
+          <t>6295; 21659</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14809; 27019</t>
+          <t>15545; 30044</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61110</t>
+          <t>66003</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>854; 7968</t>
+          <t>887; 7995</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3089; 14249</t>
+          <t>3182; 14551</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5085; 16395</t>
+          <t>5130; 16313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10552; 22156</t>
+          <t>10915; 22962</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5267; 18327</t>
+          <t>5244; 19030</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20218; 40510</t>
+          <t>19684; 41665</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16480; 39014</t>
+          <t>16272; 40246</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37689; 56308</t>
+          <t>41110; 59639</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8667; 23499</t>
+          <t>7866; 23003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25556; 49965</t>
+          <t>26208; 49401</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25946; 51109</t>
+          <t>25617; 50892</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50999; 71897</t>
+          <t>55311; 78774</t>
         </is>
       </c>
     </row>
